--- a/docs/user.xlsx
+++ b/docs/user.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nckh-tdc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nckh-tdc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFDD0DC-78FA-48CF-A118-EDADEA474047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0D2989-C611-4D07-BE5A-9BD8948F50CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5CB35C19-53DB-4FD7-B62D-7A4B604B7D4B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="users" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,44 +39,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
   <si>
     <t>tk</t>
   </si>
   <si>
-    <t>mk</t>
-  </si>
-  <si>
     <t>role</t>
   </si>
   <si>
-    <t>23211TT1111</t>
-  </si>
-  <si>
-    <t>23211TT2222</t>
-  </si>
-  <si>
-    <t>23211TT2984</t>
-  </si>
-  <si>
     <t>major</t>
   </si>
   <si>
-    <t>23211TT3333</t>
-  </si>
-  <si>
-    <t>GV001</t>
-  </si>
-  <si>
-    <t>GV002</t>
-  </si>
-  <si>
-    <t>GV003</t>
-  </si>
-  <si>
-    <t>GV004</t>
-  </si>
-  <si>
     <t>AI</t>
   </si>
   <si>
@@ -93,13 +66,49 @@
   </si>
   <si>
     <t>teacher</t>
+  </si>
+  <si>
+    <t>23211CNTT1</t>
+  </si>
+  <si>
+    <t>23211CNTT5</t>
+  </si>
+  <si>
+    <t>23211AI2</t>
+  </si>
+  <si>
+    <t>23211MMT3</t>
+  </si>
+  <si>
+    <t>23211TKDH4</t>
+  </si>
+  <si>
+    <t>GVAI</t>
+  </si>
+  <si>
+    <t>GVCNTT</t>
+  </si>
+  <si>
+    <t>GVMMT</t>
+  </si>
+  <si>
+    <t>GVTKDH</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>passwrod: 12345678</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,8 +116,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -117,37 +134,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
+        <fgColor rgb="FFD9D9D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -179,14 +166,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,138 +505,140 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2624A848-4CA6-4EE0-BBD5-1B8A412BC6D6}">
-  <dimension ref="D4:G12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="22.88671875" customWidth="1"/>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" customWidth="1"/>
+    <col min="3" max="4" width="10.77734375" customWidth="1"/>
     <col min="5" max="5" width="18.44140625" customWidth="1"/>
     <col min="6" max="6" width="27.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D4" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D5" s="4" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="4">
-        <v>12345678</v>
-      </c>
-      <c r="F5" s="5" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="6">
-        <v>12345678</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D7" s="3" t="s">
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="3">
-        <v>12345678</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2">
-        <v>12345678</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D9" s="3" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="3">
-        <v>12345678</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4">
-        <v>12345678</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2">
-        <v>12345678</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="4:7" x14ac:dyDescent="0.3">
-      <c r="D12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="6">
-        <v>12345678</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>15</v>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
